--- a/AAII_Financials/Quarterly/HOOD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HOOD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>HOOD</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1308000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1067000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1283000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1274000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>989000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>927000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1014000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>637000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>682000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>618000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>471000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>467000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>486000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>441000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>380000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>361000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>318000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>299000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>362700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>364900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>565300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>522200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>317500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>269500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>244200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>127600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>72200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>77500</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E9" s="3">
         <v>98000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>94000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>89000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>77000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>81000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>79000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>66000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>68000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>63000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>29000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>80000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>75000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>78000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>85000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>33000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>30000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>44000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>37800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>41000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>30600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>31400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>28600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>20400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1189000</v>
+      </c>
+      <c r="E10" s="3">
         <v>969000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1189000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1185000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>912000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>846000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>935000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>571000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>614000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>555000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>442000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>387000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>411000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>363000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>295000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>328000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>288000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>273000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>336200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>320900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>527500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>481200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>286900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>238100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>215600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>107200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>58800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>256000</v>
+      </c>
+      <c r="E12" s="3">
         <v>241000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>232000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>237000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>214000</v>
       </c>
       <c r="H12" s="3">
         <v>214000</v>
       </c>
       <c r="I12" s="3">
+        <v>214000</v>
+      </c>
+      <c r="J12" s="3">
         <v>208000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>205000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>209000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>196000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>197000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>202000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>207000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>199000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>183000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>185000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>244000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>266000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>280400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>679200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>156300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>116900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>82000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>55500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>45000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>33200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>30800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>29600</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1242,13 +1259,16 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>16</v>
+      <c r="D14" s="3">
+        <v>-129000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>16</v>
@@ -1274,35 +1294,35 @@
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="3">
         <v>-75000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>21000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R14" s="3">
         <v>-2000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>47000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1328,8 +1348,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1340,41 +1363,41 @@
         <v>23000</v>
       </c>
       <c r="F15" s="3">
+        <v>23000</v>
+      </c>
+      <c r="G15" s="3">
         <v>22000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>21000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>20000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>22000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>20000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>18000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>17000</v>
       </c>
       <c r="M15" s="3">
         <v>17000</v>
       </c>
       <c r="N15" s="3">
+        <v>17000</v>
+      </c>
+      <c r="O15" s="3">
         <v>19000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>15000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>20000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1414,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>734000</v>
+      </c>
+      <c r="E17" s="3">
         <v>656000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>633000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>639000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>550000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>557000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>458000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>486000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>493000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>460000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>520000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>519000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>466000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>950000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>534000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>535000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>610000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>690000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>783100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1708500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>500700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>463800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>298400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>280500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>186200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>180000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>117500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>115700</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>574000</v>
+      </c>
+      <c r="E18" s="3">
         <v>411000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>650000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>635000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>439000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>370000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>556000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>151000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>189000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>158000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-49000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-52000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-509000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-154000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-174000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-292000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-391000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-420400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1343600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>64600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>58400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>19100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>58000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-52400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-45300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-38200</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1647,28 +1680,29 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="3">
         <v>-11000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-2000</v>
       </c>
       <c r="J20" s="3">
         <v>-2000</v>
@@ -1677,150 +1711,156 @@
         <v>-2000</v>
       </c>
       <c r="L20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="M20" s="3">
         <v>-4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R20" s="3">
         <v>-14000</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-2000</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-23400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-528700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1491400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-200</v>
       </c>
       <c r="AC20" s="3">
         <v>-200</v>
       </c>
       <c r="AD20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>603000</v>
+      </c>
+      <c r="E21" s="3">
         <v>434000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>684000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>656000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>463000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>391000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>580000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>173000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>209000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>179000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-29000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-35000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>37000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-489000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-151000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-159000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-277000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-379000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-410500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1359900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-459300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1429200</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-50900</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1863,8 +1903,8 @@
       <c r="P22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1905,141 +1945,147 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>709000</v>
+      </c>
+      <c r="E23" s="3">
         <v>411000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>661000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>634000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>442000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>371000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>558000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>153000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>191000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>162000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>29000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-75000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>22000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-509000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-168000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-174000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-294000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-391000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-420300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1366900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-464200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1433000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>19300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>58100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-52600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-45500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-38500</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E24" s="3">
         <v>65000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>56000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>78000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>56000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>35000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-358000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>3000</v>
       </c>
       <c r="K24" s="3">
         <v>3000</v>
       </c>
       <c r="L24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M24" s="3">
         <v>5000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>1000</v>
       </c>
       <c r="S24" s="3">
         <v>1000</v>
@@ -2048,37 +2094,40 @@
         <v>1000</v>
       </c>
       <c r="U24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V24" s="3">
         <v>3000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-50200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>37500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>11800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>573000</v>
+      </c>
+      <c r="E26" s="3">
         <v>346000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>605000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>556000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>386000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>336000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>916000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>150000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>188000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>157000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>30000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-85000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>25000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-511000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-166000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-175000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-295000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-392000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-423300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1316700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-501700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1444800</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-52500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-44600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-38400</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E27" s="3">
         <v>350000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>605000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>556000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>386000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>336000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>916000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>150000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>188000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>157000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>30000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-85000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>25000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-511000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-166000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-175000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-295000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-392000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-423300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1316700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-501700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1444800</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-52500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-44600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-38400</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,28 +2746,31 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="3">
         <v>11000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2000</v>
       </c>
       <c r="J32" s="3">
         <v>2000</v>
@@ -2709,150 +2779,156 @@
         <v>2000</v>
       </c>
       <c r="L32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M32" s="3">
         <v>4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R32" s="3">
         <v>14000</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>2000</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>23400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>528700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1491400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>200</v>
       </c>
       <c r="AC32" s="3">
         <v>200</v>
       </c>
       <c r="AD32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E33" s="3">
         <v>350000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>605000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>556000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>386000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>336000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>916000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>150000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>188000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>157000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>30000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-85000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>25000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-511000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-166000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-175000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-295000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-392000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-423300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1316700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-501700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1444800</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-52500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-44600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-38400</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E35" s="3">
         <v>350000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>605000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>556000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>386000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>336000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>916000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>150000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>188000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>157000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>30000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-85000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>25000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-511000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-166000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-175000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-295000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-392000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-423300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1316700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-501700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1444800</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-52500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-44600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-38400</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,77 +3264,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5362000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5012000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4261000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4331000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4162000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4416000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4332000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4611000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4524000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4717000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4835000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4889000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5829000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5459000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9334000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9141000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9382000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10649000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10245900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10635000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10452300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7844100</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3264,77 +3351,80 @@
       <c r="AD41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>18543000</v>
+      </c>
+      <c r="E42" s="3">
         <v>14258000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8385000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15073000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>15113000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8570000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7975000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9265000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6801000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6639000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6050000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4660000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5189000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5066000</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R42" s="3">
+      <c r="R42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S42" s="3">
         <v>32000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>46000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>40000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>27200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>22800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>18900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>28400</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3350,77 +3440,80 @@
       <c r="AD42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>23611000</v>
+      </c>
+      <c r="E43" s="3">
         <v>18778000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>18605000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15095000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10274000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9434000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9004000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5791000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5239000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4676000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3671000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3767000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3430000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3264000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3294000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4121000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4235000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5339000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6727200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6224500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5633400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5542500</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3436,8 +3529,11 @@
       <c r="AD43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3480,8 +3576,8 @@
       <c r="P44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3522,77 +3618,80 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2204000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1472000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1206000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1729000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>995000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>989000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>846000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>20143000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21559000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>26960000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>475000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10654000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11928000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11891000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10289000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10851000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10382000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2327000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2283200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1967500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1796200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1552200</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3608,77 +3707,80 @@
       <c r="AD45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>49768000</v>
+      </c>
+      <c r="E46" s="3">
         <v>39594000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32523000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>36296000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>30616000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23492000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22175000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>39877000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>38192000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>43075000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15077000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23971000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>26376000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>25680000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>22917000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>24145000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>24045000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18355000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>19283500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18849700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17900900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14967200</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3694,53 +3796,56 @@
       <c r="AD46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4784000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4142000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4014000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3683000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3217000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2723000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2928000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2728000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2516000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2480000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2078000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1886000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1895000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1703000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3750,8 +3855,8 @@
       <c r="T47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3780,77 +3885,80 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>352000</v>
+      </c>
+      <c r="E48" s="3">
         <v>343000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>336000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>245000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>248000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>238000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>233000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>196000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>189000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>192000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>188000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>215000</v>
       </c>
       <c r="O48" s="3">
         <v>215000</v>
       </c>
       <c r="P48" s="3">
+        <v>215000</v>
+      </c>
+      <c r="Q48" s="3">
         <v>224000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>238000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>251000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>298000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>321000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>275800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>272800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>145800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>109400</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3866,71 +3974,74 @@
       <c r="AD48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>762000</v>
+      </c>
+      <c r="E49" s="3">
         <v>604000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>553000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>558000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>574000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>401000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>217000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>218000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>224000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>221000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>223000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>217000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>121000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>123000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>125000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>127000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>130000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>132000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>134600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>130800</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3946,14 +4057,17 @@
       <c r="AB49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,77 +4241,80 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>884000</v>
+      </c>
+      <c r="E52" s="3">
         <v>791000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>711000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>670000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>669000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>663000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>634000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>226000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>225000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>120000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>58000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>29000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>53000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>55000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>57000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>78000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>75000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>64000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>75200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>64100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>41900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>27800</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4210,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,77 +4419,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>56550000</v>
+      </c>
+      <c r="E54" s="3">
         <v>45474000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>38137000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>41452000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>35324000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27517000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26187000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>43245000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>41346000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>46088000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17624000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26318000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>28660000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27785000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>23337000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>24601000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>24548000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>18872000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>19769200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>19317400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18088600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15104500</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4382,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,77 +4576,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17845000</v>
+      </c>
+      <c r="E57" s="3">
         <v>17259000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12408000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12675000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10840000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7396000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7805000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6707000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6141000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6425000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5449000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4698000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5347000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5189000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4886000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5599000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6038000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7398000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6728000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7048300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8061000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6072100</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4532,74 +4663,77 @@
       <c r="AD57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>20556000</v>
+      </c>
+      <c r="E58" s="3">
         <v>13408000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12250000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>16066000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12898000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9276000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7615000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7422000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5128000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4253000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3567000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3265000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3004000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2632000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1834000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1423000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1367000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2151000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3651000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3129700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2642900</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
         <v>0</v>
       </c>
@@ -4618,77 +4752,80 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6175000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4887000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4113000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4021000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3384000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2759000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2684000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>21829000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22871000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>28435000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1821000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11685000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13005000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12796000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9533000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10487000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9994000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2032000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1968300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1620500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1536300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3236900</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4704,77 +4841,80 @@
       <c r="AD59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>44576000</v>
+      </c>
+      <c r="E60" s="3">
         <v>35554000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28771000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32762000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27122000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19431000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18104000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35958000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34140000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>39113000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10837000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19648000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21356000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>20617000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16253000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>17509000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>17399000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11581000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12347300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11798400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12240300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9308900</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4790,53 +4930,56 @@
       <c r="AD60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2369000</v>
+      </c>
+      <c r="E61" s="3">
         <v>202000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>199000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>108000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>112000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>113000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>110000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>78000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>84000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>89000</v>
       </c>
       <c r="M61" s="3">
         <v>89000</v>
       </c>
       <c r="N61" s="3">
+        <v>89000</v>
+      </c>
+      <c r="O61" s="3">
         <v>95000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>116000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>120000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4853,14 +4996,14 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>5189800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4675100</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4876,77 +5019,80 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E62" s="3">
         <v>23000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>5000</v>
       </c>
       <c r="H62" s="3">
         <v>5000</v>
       </c>
       <c r="I62" s="3">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="J62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
+      <c r="L62" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="M62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N62" s="3">
         <v>2000</v>
-      </c>
-      <c r="N62" s="3">
-        <v>1000</v>
       </c>
       <c r="O62" s="3">
         <v>1000</v>
       </c>
       <c r="P62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q62" s="3">
         <v>2000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>127900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>137100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>131100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>159100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>128700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>134400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>463500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>425900</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,77 +5375,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>47009000</v>
+      </c>
+      <c r="E66" s="3">
         <v>35786000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>28986000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32885000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>27252000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19564000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18215000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>36037000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>34224000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>39203000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10928000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19744000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21473000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20739000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16380900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17646100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17530100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11740100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12476100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11932800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17893600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14409900</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5306,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5573,13 +5741,13 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
-        <v>2179700</v>
+        <v>0</v>
       </c>
       <c r="X70" s="3">
         <v>2179700</v>
       </c>
       <c r="Y70" s="3">
-        <v>0</v>
+        <v>2179700</v>
       </c>
       <c r="Z70" s="3">
         <v>0</v>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,77 +5853,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1241000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1802000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2152000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2757000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3313000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3699000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-4035000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-4951000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5101000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5289000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5446000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5476000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5391000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5416000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-4905000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-4739000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-4564000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-4269000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3876500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3453300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2136600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1634900</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5768,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,77 +6209,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9480000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9319000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9140000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8567000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8072000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7953000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7972000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7208000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7122000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6885000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6696000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6574000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7187000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7046000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6956100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6954900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7017900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7131900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7293100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7384600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-1984800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-1485200</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6112,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E81" s="3">
         <v>350000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>605000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>556000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>386000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>336000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>916000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>150000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>188000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>157000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>30000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-85000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>25000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-511000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-166000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-175000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-295000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-392000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-423300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1316700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-501700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1444800</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-52500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-44600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-38400</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,77 +6605,78 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E83" s="3">
         <v>20000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-21000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>20000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>18000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>17000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-24000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>19000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>15000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>17000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>17000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>15000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>17000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3800</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6493,8 +6692,11 @@
       <c r="AD83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,77 +7137,80 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>720000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2038000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-937000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1576000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3509000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>642000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1400000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1812000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>54000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-623000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>960000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-977000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>370000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>828000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>181000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-207000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1263000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>437000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-275600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1008300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2281300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1882200</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>16</v>
       </c>
@@ -7009,8 +7226,11 @@
       <c r="AD89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,77 +7261,78 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-2000</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-1000</v>
       </c>
       <c r="N91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>16</v>
+      <c r="O91" s="3">
+        <v>-1000</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R91" s="3">
         <v>-10000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-14000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-21000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-24900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-30900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-12800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>16</v>
       </c>
@@ -7127,8 +7348,11 @@
       <c r="AD91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,77 +7526,80 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-770000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-284000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-558000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-142000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>832000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>9000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>34000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-123000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-47000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-97000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-481000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>11000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-26000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-34000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-58400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-151600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-16500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7385,8 +7615,11 @@
       <c r="AD94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7461,8 +7695,8 @@
       <c r="P96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,77 +8004,80 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1906000</v>
+      </c>
+      <c r="E100" s="3">
         <v>180000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>118000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-286000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-417000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-178000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-95000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-42000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-30000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-615000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1000</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-6100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1650800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3557800</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7847,23 +8093,26 @@
       <c r="AD100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E101" s="3">
         <v>1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>16</v>
       </c>
@@ -7879,44 +8128,44 @@
       <c r="L101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>16</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>16</v>
+      <c r="Y101" s="3">
+        <v>0</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>16</v>
@@ -7933,77 +8182,80 @@
       <c r="AD101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1853000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1928000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1376000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1723000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4062000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>235000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1546000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1595000</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-700000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>966000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1689000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>376000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>336000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>193000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-221000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1288000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>403000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-340100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>490800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2265700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1664200</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>16</v>
       </c>
@@ -8017,6 +8269,9 @@
         <v>16</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>16</v>
       </c>
     </row>
